--- a/data/trans_orig/IMC_inf_MED_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Estudios-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15351</v>
+        <v>18591</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>10488</v>
+        <v>13098</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>21395</v>
+        <v>25098</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2697868897876032</v>
+        <v>0.2453516141026484</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1843338404266488</v>
+        <v>0.1728613541226593</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3760243059318696</v>
+        <v>0.3312314717598057</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>14239</v>
+        <v>15541</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>9513</v>
+        <v>10393</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>19954</v>
+        <v>21820</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2160504150119885</v>
+        <v>0.1928872995419658</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1443470013638928</v>
+        <v>0.1289971553595373</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3027629826629089</v>
+        <v>0.2708125958389401</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>29590</v>
+        <v>34132</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>22495</v>
+        <v>26150</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>38350</v>
+        <v>43708</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.240948064241383</v>
+        <v>0.2183144195009455</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1831767518522177</v>
+        <v>0.1672593484848563</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3122810185984908</v>
+        <v>0.2795625211934821</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>41548</v>
+        <v>57182</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35504</v>
+        <v>50675</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>46411</v>
+        <v>62675</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7302131102123969</v>
+        <v>0.7546483858973516</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6239756940681305</v>
+        <v>0.6687685282401943</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8156661595733512</v>
+        <v>0.8271386458773408</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>51667</v>
+        <v>65030</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>45952</v>
+        <v>58751</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>56393</v>
+        <v>70178</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7839495849880115</v>
+        <v>0.8071127004580342</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6972370173370911</v>
+        <v>0.7291874041610595</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8556529986361073</v>
+        <v>0.8710028446404626</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>93215</v>
+        <v>122211</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>84455</v>
+        <v>112635</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>100310</v>
+        <v>130193</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7590519357586171</v>
+        <v>0.7816855804990546</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6877189814015091</v>
+        <v>0.7204374788065179</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8168232481477823</v>
+        <v>0.8327406515151436</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>102826</v>
+        <v>113014</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>89144</v>
+        <v>98178</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>118196</v>
+        <v>128205</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2967162975150009</v>
+        <v>0.2748833697364035</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2572349030892979</v>
+        <v>0.2387972576418479</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.341068908620047</v>
+        <v>0.3118328254337757</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>72540</v>
+        <v>84647</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>61738</v>
+        <v>71337</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>85394</v>
+        <v>98335</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2290067899593227</v>
+        <v>0.2246824811421367</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1949043245057975</v>
+        <v>0.189353959494261</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2695837248274655</v>
+        <v>0.2610154143959589</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>175366</v>
+        <v>197661</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>157895</v>
+        <v>178696</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>195919</v>
+        <v>221071</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.264381751062037</v>
+        <v>0.2508786405871642</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2380426157967588</v>
+        <v>0.2268073980453173</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2953679838676471</v>
+        <v>0.2805916244082707</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>353</v>
+        <v>432</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>243720</v>
+        <v>298121</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>228350</v>
+        <v>282930</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>257402</v>
+        <v>312957</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7032837024849991</v>
+        <v>0.7251166302635965</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6589310913799531</v>
+        <v>0.6881671745662242</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7427650969107021</v>
+        <v>0.7612027423581522</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>244221</v>
+        <v>292094</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>231367</v>
+        <v>278406</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>255023</v>
+        <v>305404</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7709932100406772</v>
+        <v>0.7753175188578634</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7304162751725349</v>
+        <v>0.7389845856040411</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8050956754942026</v>
+        <v>0.810646040505739</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>705</v>
+        <v>853</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>487940</v>
+        <v>590215</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>467387</v>
+        <v>566805</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>505411</v>
+        <v>609180</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7356182489379629</v>
+        <v>0.7491213594128359</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7046320161323529</v>
+        <v>0.7194083755917293</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7619573842032411</v>
+        <v>0.7731926019546831</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>957</v>
+        <v>1134</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>28703</v>
+        <v>30178</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>21206</v>
+        <v>22342</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>36857</v>
+        <v>38494</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2409044225629987</v>
+        <v>0.2181792186523086</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1779772052707136</v>
+        <v>0.1615254975785956</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3093407452875923</v>
+        <v>0.2783018572324175</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>22428</v>
+        <v>25148</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>15598</v>
+        <v>17463</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>29754</v>
+        <v>33757</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1900588478793153</v>
+        <v>0.1810806414793902</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.132182226997245</v>
+        <v>0.1257451191098143</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.252148140810452</v>
+        <v>0.243073145192523</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>51131</v>
+        <v>55326</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>41744</v>
+        <v>44984</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>62042</v>
+        <v>67870</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2156043471214577</v>
+        <v>0.1995925757920209</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1760200720398474</v>
+        <v>0.1622817861940415</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2616136504836925</v>
+        <v>0.2448459612357383</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>90445</v>
+        <v>108140</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>82291</v>
+        <v>99824</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>97942</v>
+        <v>115976</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7590955774370013</v>
+        <v>0.7818207813476914</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6906592547124079</v>
+        <v>0.7216981427675826</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8220227947292864</v>
+        <v>0.8384745024214046</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>95575</v>
+        <v>113728</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>88249</v>
+        <v>105119</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>102405</v>
+        <v>121413</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8099411521206847</v>
+        <v>0.8189193585206098</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7478518591895481</v>
+        <v>0.7569268548074777</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8678177730027553</v>
+        <v>0.874254880890186</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>186021</v>
+        <v>221868</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>175110</v>
+        <v>209324</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>195408</v>
+        <v>232210</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.7843956528785423</v>
+        <v>0.8004074242079791</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7383863495163075</v>
+        <v>0.7551540387642617</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8239799279601527</v>
+        <v>0.8377182138059583</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>130936</v>
+        <v>144689</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>163775</v>
+        <v>180627</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2810594781674127</v>
+        <v>0.2587597419028065</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2505511104084192</v>
+        <v>0.2314193338361696</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3133893808194827</v>
+        <v>0.2888995095664735</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>234185</v>
+        <v>263426</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>279826</v>
+        <v>312007</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2502647366916653</v>
+        <v>0.2350712253584804</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2288614800298711</v>
+        <v>0.2156727653489396</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2734644421752407</v>
+        <v>0.2554472329920764</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>543</v>
+        <v>668</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>375713</v>
+        <v>463442</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>358818</v>
+        <v>444598</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>391657</v>
+        <v>480536</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7189405218325873</v>
+        <v>0.7412402580971935</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6866106191805172</v>
+        <v>0.7111004904335265</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7494488895915807</v>
+        <v>0.7685806661638306</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>560</v>
+        <v>675</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>391463</v>
+        <v>470852</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>376138</v>
+        <v>453484</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>406034</v>
+        <v>486328</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7818784110556219</v>
+        <v>0.7897710310928593</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.751269520370661</v>
+        <v>0.7606396882115134</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8109815397538159</v>
+        <v>0.8157294332148085</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>1103</v>
+        <v>1343</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>767176</v>
+        <v>934294</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>743437</v>
+        <v>909406</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>789078</v>
+        <v>957987</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7497352633083347</v>
+        <v>0.7649287746415195</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7265355578247593</v>
+        <v>0.7445527670079238</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7711385199701289</v>
+        <v>0.7843272346510604</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>751</v>
+        <v>895</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1469</v>
+        <v>1749</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1828,67 +1828,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11609</v>
+        <v>13431</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7216</v>
+        <v>8885</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>16724</v>
+        <v>19301</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2367804882764704</v>
+        <v>0.2050432413659233</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1471836650798361</v>
+        <v>0.1356495079894939</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3411054913717556</v>
+        <v>0.2946623384939361</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>8817</v>
+        <v>9417</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>5158</v>
+        <v>5413</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>14274</v>
+        <v>14337</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2290134171815054</v>
+        <v>0.1831492391143975</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1339722316586565</v>
+        <v>0.1052743513897078</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3707514198883032</v>
+        <v>0.2788323867863247</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>20426</v>
+        <v>22848</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>14247</v>
+        <v>16433</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>27169</v>
+        <v>31208</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2333641861740443</v>
+        <v>0.1954147610513214</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1627691202218707</v>
+        <v>0.1405445706352267</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3104003281570981</v>
+        <v>0.266915908774556</v>
       </c>
     </row>
     <row r="5">
@@ -1899,67 +1899,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>37420</v>
+        <v>52071</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>32305</v>
+        <v>46201</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>41813</v>
+        <v>56617</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7632195117235296</v>
+        <v>0.7949567586340767</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6588945086282444</v>
+        <v>0.7053376615060638</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8528163349201638</v>
+        <v>0.8643504920105061</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>29682</v>
+        <v>42002</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>24225</v>
+        <v>37082</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>33341</v>
+        <v>46006</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7709865828184946</v>
+        <v>0.8168507608856025</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6292485801116967</v>
+        <v>0.7211676132136764</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8660277683413435</v>
+        <v>0.8947256486102922</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>67102</v>
+        <v>94073</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>60359</v>
+        <v>85713</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>73281</v>
+        <v>100488</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7666358138259557</v>
+        <v>0.8045852389486786</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6895996718429018</v>
+        <v>0.7330840912254437</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8372308797781293</v>
+        <v>0.8594554293647729</v>
       </c>
     </row>
     <row r="6">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -1991,16 +1991,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2012,16 +2012,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2045,67 +2045,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>81810</v>
+        <v>94639</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>69390</v>
+        <v>81034</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>94859</v>
+        <v>109743</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2297374652403917</v>
+        <v>0.225888631344264</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1948617247385736</v>
+        <v>0.1934149216394691</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2663825861743778</v>
+        <v>0.2619384822641451</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>43171</v>
+        <v>45837</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>33995</v>
+        <v>36776</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>54055</v>
+        <v>57693</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1281733092405487</v>
+        <v>0.1176853673456414</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.100929923861058</v>
+        <v>0.09442139040811647</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1604881522893255</v>
+        <v>0.1481244192088572</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>124980</v>
+        <v>140476</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>109839</v>
+        <v>124339</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>140549</v>
+        <v>159768</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1803686956288567</v>
+        <v>0.1737595116426006</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1585172348167566</v>
+        <v>0.1537993078524299</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2028377877151161</v>
+        <v>0.1976232286989918</v>
       </c>
     </row>
     <row r="8">
@@ -2116,67 +2116,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>386</v>
+        <v>458</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>274290</v>
+        <v>324324</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>261241</v>
+        <v>309220</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>286710</v>
+        <v>337929</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7702625347596083</v>
+        <v>0.774111368655736</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7336174138256222</v>
+        <v>0.7380615177358548</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8051382752614263</v>
+        <v>0.8065850783605308</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>436</v>
+        <v>514</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>293644</v>
+        <v>343650</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>282760</v>
+        <v>331794</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>302820</v>
+        <v>352711</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8718266907594513</v>
+        <v>0.8823146326543586</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8395118477106746</v>
+        <v>0.8518755807911423</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8990700761389422</v>
+        <v>0.9055786095918835</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>822</v>
+        <v>972</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>567935</v>
+        <v>667974</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>552366</v>
+        <v>648682</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>583076</v>
+        <v>684111</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8196313043711433</v>
+        <v>0.8262404883573994</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7971622122848837</v>
+        <v>0.8023767713010082</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8414827651832433</v>
+        <v>0.8462006921475701</v>
       </c>
     </row>
     <row r="9">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>503</v>
+        <v>592</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2208,16 +2208,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>502</v>
+        <v>584</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2229,16 +2229,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1005</v>
+        <v>1176</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2262,67 +2262,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>19149</v>
+        <v>19912</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>13598</v>
+        <v>13576</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>27347</v>
+        <v>26860</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1607892148553552</v>
+        <v>0.1354240490576121</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1141798401160793</v>
+        <v>0.09233139325303784</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2296252850385614</v>
+        <v>0.18267893125157</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15826</v>
+        <v>18809</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>10776</v>
+        <v>12917</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>23040</v>
+        <v>25957</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1414506697024728</v>
+        <v>0.1377097425669956</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.09631290075288165</v>
+        <v>0.09456756391151505</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2059235416234743</v>
+        <v>0.1900422851931999</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>34975</v>
+        <v>38721</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>26390</v>
+        <v>30848</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>44537</v>
+        <v>50964</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.151421643783798</v>
+        <v>0.1365247886278317</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1142533111999823</v>
+        <v>0.1087634343135501</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.192818539617634</v>
+        <v>0.1796919047155046</v>
       </c>
     </row>
     <row r="11">
@@ -2333,67 +2333,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>99943</v>
+        <v>127123</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>91745</v>
+        <v>120175</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>105494</v>
+        <v>133459</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8392107851446448</v>
+        <v>0.8645759509423879</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7703747149614382</v>
+        <v>0.8173210687484302</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8858201598839205</v>
+        <v>0.9076686067469623</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>96059</v>
+        <v>117776</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>88845</v>
+        <v>110628</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>101109</v>
+        <v>123668</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8585493302975272</v>
+        <v>0.8622902574330045</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7940764583765253</v>
+        <v>0.8099577148067999</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9036870992471178</v>
+        <v>0.9054324360884849</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>196002</v>
+        <v>244900</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>186440</v>
+        <v>232657</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>204587</v>
+        <v>252773</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8485783562162019</v>
+        <v>0.8634752113721683</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.8071814603823662</v>
+        <v>0.8203080952844954</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8857466888000178</v>
+        <v>0.8912365656864499</v>
       </c>
     </row>
     <row r="12">
@@ -2404,16 +2404,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2425,16 +2425,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2446,16 +2446,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>339</v>
+        <v>416</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2479,67 +2479,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
     </row>
     <row r="14">
@@ -2550,67 +2550,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>411654</v>
+        <v>503518</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>394145</v>
+        <v>486846</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>426142</v>
+        <v>519884</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7852674041870716</v>
+        <v>0.7973368498449566</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7518675057711615</v>
+        <v>0.770935390738322</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8129059335301964</v>
+        <v>0.8232526649192942</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>622</v>
+        <v>750</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>419385</v>
+        <v>503428</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>404796</v>
+        <v>490720</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>429930</v>
+        <v>516279</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8608091036769272</v>
+        <v>0.8717497285048019</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8308633544692922</v>
+        <v>0.8497439617399838</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8824529067628336</v>
+        <v>0.8940024716918201</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>1206</v>
+        <v>1465</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>831040</v>
+        <v>1006948</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>809671</v>
+        <v>984702</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>849655</v>
+        <v>1027145</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8216556901691411</v>
+        <v>0.832881204714476</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.8005280405636144</v>
+        <v>0.8144813257376206</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8400605390096288</v>
+        <v>0.849587092610023</v>
       </c>
     </row>
     <row r="15">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2642,16 +2642,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2663,16 +2663,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2743,7 +2743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2948,46 +2948,46 @@
         <v>0.3524162045190609</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1620</v>
+        <v>3012</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>394</v>
+        <v>1115</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4858</v>
+        <v>6436</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.09736959081109881</v>
+        <v>0.1562371040635662</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.02369520949375807</v>
+        <v>0.05783610223089332</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2920423664243431</v>
+        <v>0.3338652948220358</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>6027</v>
+        <v>7419</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>2928</v>
+        <v>3928</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>10896</v>
+        <v>12898</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.14643087905149</v>
+        <v>0.1693778778595711</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.071133721668448</v>
+        <v>0.08968601638465248</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2647422697182116</v>
+        <v>0.2944651159708576</v>
       </c>
     </row>
     <row r="5">
@@ -3019,46 +3019,46 @@
         <v>0.9278098611599557</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>15014</v>
+        <v>16265</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11776</v>
+        <v>12841</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>16240</v>
+        <v>18162</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.9026304091889011</v>
+        <v>0.8437628959364343</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7079576335756574</v>
+        <v>0.6661347051779644</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.9763047905062417</v>
+        <v>0.9421638977691066</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>35131</v>
+        <v>36382</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>30262</v>
+        <v>30903</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>38230</v>
+        <v>39873</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.85356912094851</v>
+        <v>0.830622122140429</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7352577302817892</v>
+        <v>0.7055348840291424</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.9288662783315519</v>
+        <v>0.9103139836153474</v>
       </c>
     </row>
     <row r="6">
@@ -3090,16 +3090,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3111,16 +3111,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3144,67 +3144,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>47173</v>
+        <v>47628</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>37692</v>
+        <v>37412</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>58886</v>
+        <v>58610</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2355112849878541</v>
+        <v>0.2263733428791819</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1881770814806643</v>
+        <v>0.1778179003016295</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.293989180434569</v>
+        <v>0.2785677453680547</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19721</v>
+        <v>20227</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13343</v>
+        <v>14682</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>26951</v>
+        <v>28513</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1304361257414428</v>
+        <v>0.1268238634202751</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.08825369640195196</v>
+        <v>0.09205922268498874</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1782563693784863</v>
+        <v>0.178775272003855</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>66894</v>
+        <v>67855</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>54690</v>
+        <v>55350</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>79457</v>
+        <v>82383</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1903138920268281</v>
+        <v>0.1834491179392568</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1555936040916557</v>
+        <v>0.1496419685188169</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2260570932711554</v>
+        <v>0.2227263851064879</v>
       </c>
     </row>
     <row r="8">
@@ -3215,67 +3215,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>153127</v>
+        <v>162768</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>141414</v>
+        <v>151786</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>162608</v>
+        <v>172984</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7644887150121461</v>
+        <v>0.7736266571208182</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7060108195654307</v>
+        <v>0.7214322546319456</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8118229185193355</v>
+        <v>0.8221820996983704</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>131471</v>
+        <v>139262</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>124241</v>
+        <v>130976</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>137849</v>
+        <v>144807</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8695638742585572</v>
+        <v>0.8731761365797248</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8217436306215137</v>
+        <v>0.8212247279961451</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9117463035980479</v>
+        <v>0.9079407773150111</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>284598</v>
+        <v>302030</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>272035</v>
+        <v>287502</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>296802</v>
+        <v>314535</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.809686107973172</v>
+        <v>0.8165508820607433</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7739429067288446</v>
+        <v>0.7772736148935121</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8444063959083443</v>
+        <v>0.8503580314811833</v>
       </c>
     </row>
     <row r="9">
@@ -3286,16 +3286,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3307,16 +3307,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3328,16 +3328,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3367,19 +3367,19 @@
         <v>7358</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3880</v>
+        <v>4094</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>12365</v>
+        <v>12939</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1043843109024222</v>
+        <v>0.09810466541518707</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.05504021530988456</v>
+        <v>0.05458049924489888</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1754158152695646</v>
+        <v>0.172512167990137</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>11</v>
@@ -3388,19 +3388,19 @@
         <v>6298</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3302</v>
+        <v>3143</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>10927</v>
+        <v>10880</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.0927567874098985</v>
+        <v>0.0907735430490304</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.04863096359135285</v>
+        <v>0.04529581373058516</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1609308347912576</v>
+        <v>0.1568210945320703</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>23</v>
@@ -3409,19 +3409,19 @@
         <v>13656</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>8508</v>
+        <v>8629</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>19812</v>
+        <v>20142</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.09867952959703892</v>
+        <v>0.09458185390574632</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.0614771900672899</v>
+        <v>0.0597630388748083</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1431629582184692</v>
+        <v>0.1395021029281398</v>
       </c>
     </row>
     <row r="11">
@@ -3432,67 +3432,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>63133</v>
+        <v>67645</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>58126</v>
+        <v>62064</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>66611</v>
+        <v>70909</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8956156890975779</v>
+        <v>0.901895334584813</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.8245841847304354</v>
+        <v>0.8274878320098629</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.9449597846901157</v>
+        <v>0.9454195007551009</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>61598</v>
+        <v>63082</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>56969</v>
+        <v>58500</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>64594</v>
+        <v>66237</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.9072432125901013</v>
+        <v>0.9092264569509695</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8390691652087424</v>
+        <v>0.8431789054679297</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9513690364086471</v>
+        <v>0.9547041862694149</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>124731</v>
+        <v>130727</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>118575</v>
+        <v>124241</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>129879</v>
+        <v>135754</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.9013204704029611</v>
+        <v>0.9054181460942535</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.8568370417815308</v>
+        <v>0.8604978970718603</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.93852280993271</v>
+        <v>0.9402369611251917</v>
       </c>
     </row>
     <row r="12">
@@ -3503,16 +3503,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3524,16 +3524,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3545,16 +3545,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3578,67 +3578,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>20610</v>
+        <v>21951</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>37054</v>
+        <v>37584</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1172497653739078</v>
+        <v>0.1190293316454167</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.08743334302902368</v>
+        <v>0.0884613013587426</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1571917747652832</v>
+        <v>0.1514604218648846</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>73709</v>
+        <v>75335</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>101058</v>
+        <v>106350</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1630330031050146</v>
+        <v>0.1593531132002171</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1388021358251922</v>
+        <v>0.1349931110562688</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.1903025231343647</v>
+        <v>0.1905684554140433</v>
       </c>
     </row>
     <row r="14">
@@ -3649,67 +3649,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>236377</v>
+        <v>250530</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>222208</v>
+        <v>236602</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>247740</v>
+        <v>261635</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.8004225467812189</v>
+        <v>0.8083609645347002</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7524447391616108</v>
+        <v>0.7634222539518554</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8389022744544455</v>
+        <v>0.8441932883604175</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>208084</v>
+        <v>218608</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>198668</v>
+        <v>210561</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>215112</v>
+        <v>226194</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8827502346260923</v>
+        <v>0.8809706683545835</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8428082252347169</v>
+        <v>0.8485395781351154</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9125666569709765</v>
+        <v>0.9115386986412574</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>631</v>
+        <v>666</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>444460</v>
+        <v>469138</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>429979</v>
+        <v>451718</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>457328</v>
+        <v>482733</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8369669968949854</v>
+        <v>0.8406468867997827</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.8096974768656355</v>
+        <v>0.8094315445859569</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8611978641748079</v>
+        <v>0.8650068889437311</v>
       </c>
     </row>
     <row r="15">
@@ -3720,16 +3720,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3741,16 +3741,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3762,16 +3762,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>765</v>
+        <v>804</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
